--- a/Template Import/Claim Paid import Draft.xlsx
+++ b/Template Import/Claim Paid import Draft.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D16D30-C07B-481D-ADC7-2D70B8CCE18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A48D02-CBD1-43B2-8F7B-FE84578AF189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{B9559F4F-8B01-4B5B-9FF7-B98A961DB515}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{B9559F4F-8B01-4B5B-9FF7-B98A961DB515}"/>
   </bookViews>
   <sheets>
     <sheet name="Claim Paid H" sheetId="1" r:id="rId1"/>
@@ -1026,23 +1026,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55974766-F69B-4F0C-852F-B6AF865E96E7}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.4140625" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.58203125" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.796875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.796875" style="6"/>
+    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1077,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1154,34 +1154,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFE5FE0-1F97-485F-93CA-EF053737A52B}">
   <dimension ref="A1:V3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.08203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.796875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.19921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
-    <col min="11" max="11" width="19.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.09765625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="41.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.69921875" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.296875" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.09765625" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="61.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.796875" style="6"/>
+    <col min="7" max="7" width="9.83203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.1640625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="19.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.08203125" style="6" customWidth="1"/>
+    <col min="13" max="13" width="41.6640625" style="6" customWidth="1"/>
+    <col min="14" max="14" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.08203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="61.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.83203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.6">
       <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.6">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.6">
       <c r="A3" s="6">
         <v>1</v>
       </c>

--- a/Template Import/Claim Paid import Draft.xlsx
+++ b/Template Import/Claim Paid import Draft.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\MSIGSX\Template Import\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33A48D02-CBD1-43B2-8F7B-FE84578AF189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5239DB58-BE21-43E5-9D83-5364681702C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{B9559F4F-8B01-4B5B-9FF7-B98A961DB515}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9559F4F-8B01-4B5B-9FF7-B98A961DB515}"/>
   </bookViews>
   <sheets>
     <sheet name="Claim Paid H" sheetId="1" r:id="rId1"/>
     <sheet name="Claim Paid L" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -369,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="94">
   <si>
     <t>DocNum</t>
   </si>
@@ -540,6 +541,117 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t>Claim Paid- HI</t>
+  </si>
+  <si>
+    <t>Claim Paid-CL</t>
+  </si>
+  <si>
+    <t>Claim Paid-Engineering</t>
+  </si>
+  <si>
+    <t>Claim Paid-FIRE</t>
+  </si>
+  <si>
+    <t>Claim Paid-IAR</t>
+  </si>
+  <si>
+    <t>Claim Paid-MISC</t>
+  </si>
+  <si>
+    <t>Claim Paid-MOC</t>
+  </si>
+  <si>
+    <t>Claim Paid-MOV</t>
+  </si>
+  <si>
+    <t>Claim Paid-MR</t>
+  </si>
+  <si>
+    <t>Claim Paid-PA</t>
+  </si>
+  <si>
+    <t>Claim Paid-Property</t>
+  </si>
+  <si>
+    <t>Claim Paid-TA</t>
+  </si>
+  <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>604.31.00</t>
+  </si>
+  <si>
+    <t>604.32.00</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ລົດ-ພາກສະໝັກໃຈ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ- ອຫ ສ່ວນບຸກຄົນ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ສຸຂະພາບ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ- ຄສ ຮອບດ້ານ ອກ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ- ຄສ ອື່ນໆ</t>
+  </si>
+  <si>
+    <t>604.33.00</t>
+  </si>
+  <si>
+    <t>604.34.00</t>
+  </si>
+  <si>
+    <t>604.35.00</t>
+  </si>
+  <si>
+    <t>604.36.00</t>
+  </si>
+  <si>
+    <t>604.37.00</t>
+  </si>
+  <si>
+    <t>604.38.00</t>
+  </si>
+  <si>
+    <t>604.39.00</t>
+  </si>
+  <si>
+    <t>604.40.00</t>
+  </si>
+  <si>
+    <t>604.41.00</t>
+  </si>
+  <si>
+    <t>604.42.00</t>
   </si>
 </sst>
 </file>
@@ -608,7 +720,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -657,6 +769,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -670,7 +788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -691,6 +809,8 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1026,23 +1146,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55974766-F69B-4F0C-852F-B6AF865E96E7}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.58203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.296875" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="6" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.83203125" style="6"/>
+    <col min="9" max="9" width="12.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.796875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1154,34 +1274,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFE5FE0-1F97-485F-93CA-EF053737A52B}">
   <dimension ref="A1:V3"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="18.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="9.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="26.4140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="9.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.09765625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.83203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="19.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.08203125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="41.6640625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="9.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.4140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.58203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.08203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="61.4140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="8.83203125" style="6"/>
+    <col min="7" max="7" width="9.796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.19921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="19.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.09765625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="41.69921875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="9.296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.296875" style="6" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.09765625" style="6" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="61.3984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1249,7 +1369,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1317,7 +1437,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1387,4 +1507,159 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5D10CE-6AB0-4859-BDE7-840ADCEFD5EE}">
+  <dimension ref="D1:H13"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="5" width="8.796875" style="12"/>
+    <col min="6" max="6" width="19.59765625" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F3" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F6" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F7" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F8" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F9" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F10" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F11" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F12" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Template Import/Claim Paid import Draft.xlsx
+++ b/Template Import/Claim Paid import Draft.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\MSIG\pregolive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\MSIGSX\Template Import\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D16D30-C07B-481D-ADC7-2D70B8CCE18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5239DB58-BE21-43E5-9D83-5364681702C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="24" yWindow="24" windowWidth="23016" windowHeight="13656" xr2:uid="{B9559F4F-8B01-4B5B-9FF7-B98A961DB515}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{B9559F4F-8B01-4B5B-9FF7-B98A961DB515}"/>
   </bookViews>
   <sheets>
     <sheet name="Claim Paid H" sheetId="1" r:id="rId1"/>
     <sheet name="Claim Paid L" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -369,7 +370,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="94">
   <si>
     <t>DocNum</t>
   </si>
@@ -540,6 +541,117 @@
   </si>
   <si>
     <t>PolicyNO</t>
+  </si>
+  <si>
+    <t>Claim Paid- HI</t>
+  </si>
+  <si>
+    <t>Claim Paid-CL</t>
+  </si>
+  <si>
+    <t>Claim Paid-Engineering</t>
+  </si>
+  <si>
+    <t>Claim Paid-FIRE</t>
+  </si>
+  <si>
+    <t>Claim Paid-IAR</t>
+  </si>
+  <si>
+    <t>Claim Paid-MISC</t>
+  </si>
+  <si>
+    <t>Claim Paid-MOC</t>
+  </si>
+  <si>
+    <t>Claim Paid-MOV</t>
+  </si>
+  <si>
+    <t>Claim Paid-MR</t>
+  </si>
+  <si>
+    <t>Claim Paid-PA</t>
+  </si>
+  <si>
+    <t>Claim Paid-Property</t>
+  </si>
+  <si>
+    <t>Claim Paid-TA</t>
+  </si>
+  <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ລົດ-ພາກບັງຄັບ</t>
+  </si>
+  <si>
+    <t>604.31.00</t>
+  </si>
+  <si>
+    <t>604.32.00</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ລົດ-ພາກສະໝັກໃຈ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ອັກຄີໄພ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ຂົນສົ່ງ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ- ອຫ ສ່ວນບຸກຄົນ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ສຸຂະພາບ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ທ່ອງທ່ຽວ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ຊັບສິນ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ- ຄສ ຮອບດ້ານ ອກ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ວິສະວະກຳ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ-ສິນເຊື່ອ</t>
+  </si>
+  <si>
+    <t>ຈ່າຍສິນທົດແທນປະກັນໄພ- ຄສ ອື່ນໆ</t>
+  </si>
+  <si>
+    <t>604.33.00</t>
+  </si>
+  <si>
+    <t>604.34.00</t>
+  </si>
+  <si>
+    <t>604.35.00</t>
+  </si>
+  <si>
+    <t>604.36.00</t>
+  </si>
+  <si>
+    <t>604.37.00</t>
+  </si>
+  <si>
+    <t>604.38.00</t>
+  </si>
+  <si>
+    <t>604.39.00</t>
+  </si>
+  <si>
+    <t>604.40.00</t>
+  </si>
+  <si>
+    <t>604.41.00</t>
+  </si>
+  <si>
+    <t>604.42.00</t>
   </si>
 </sst>
 </file>
@@ -608,7 +720,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -657,6 +769,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -670,7 +788,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -691,6 +809,8 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1026,7 +1146,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55974766-F69B-4F0C-852F-B6AF865E96E7}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.3984375" style="6" bestFit="1" customWidth="1"/>
@@ -1042,7 +1162,7 @@
     <col min="12" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1077,7 +1197,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1232,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1154,7 +1274,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EFE5FE0-1F97-485F-93CA-EF053737A52B}">
   <dimension ref="A1:V3"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="19.2" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="12.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.09765625" style="6" customWidth="1"/>
@@ -1168,7 +1288,7 @@
     <col min="10" max="10" width="17.19921875" style="6" customWidth="1"/>
     <col min="11" max="11" width="19.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.09765625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="41.69921875" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="41.69921875" style="6" customWidth="1"/>
     <col min="14" max="14" width="9.296875" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.3984375" style="6" bestFit="1" customWidth="1"/>
@@ -1181,7 +1301,7 @@
     <col min="23" max="16384" width="8.796875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="13" t="s">
         <v>13</v>
       </c>
@@ -1249,7 +1369,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="7" t="s">
         <v>0</v>
       </c>
@@ -1317,7 +1437,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -1387,4 +1507,159 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A5D10CE-6AB0-4859-BDE7-840ADCEFD5EE}">
+  <dimension ref="D1:H13"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="5" width="8.796875" style="12"/>
+    <col min="6" max="6" width="19.59765625" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="8.796875" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F2" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F3" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F4" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F5" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F6" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F7" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F8" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F9" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F10" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F11" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F12" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="13" spans="4:8" x14ac:dyDescent="0.5">
+      <c r="F13" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>83</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>